--- a/artfynd/A 21730-2025 artfynd.xlsx
+++ b/artfynd/A 21730-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105928497</v>
+        <v>105928522</v>
       </c>
       <c r="B2" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,27 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>690810.3171372488</v>
+        <v>690932</v>
       </c>
       <c r="R2" t="n">
-        <v>6625335.754432246</v>
+        <v>6625303</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +746,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105928522</v>
+        <v>105928496</v>
       </c>
       <c r="B3" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,26 +791,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -839,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>690931.9480205297</v>
+        <v>690831</v>
       </c>
       <c r="R3" t="n">
-        <v>6625303.078101497</v>
+        <v>6625395</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,19 +851,14 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Mindre exemplar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,7 +879,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna Broberg</t>
+          <t>Max Ljungkvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -916,15 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105928355</v>
+        <v>105928497</v>
       </c>
       <c r="B4" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -932,21 +901,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -960,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>690918.7851298833</v>
+        <v>690811</v>
       </c>
       <c r="R4" t="n">
-        <v>6625313.014637181</v>
+        <v>6625336</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,19 +962,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,15 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105928496</v>
+        <v>105928350</v>
       </c>
       <c r="B5" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104803</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1053,24 +1007,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>220461</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Skogsbräsma</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cardamine flexuosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>With.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1080,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>690831.0756102945</v>
+        <v>690996</v>
       </c>
       <c r="R5" t="n">
-        <v>6625394.924160354</v>
+        <v>6625304</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,24 +1068,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Mindre exemplar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,7 +1091,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Max Ljungkvist</t>
+          <t>Anna Broberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1162,15 +1102,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105928356</v>
+        <v>105928351</v>
       </c>
       <c r="B6" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1206,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>690935.6792742953</v>
+        <v>690872</v>
       </c>
       <c r="R6" t="n">
-        <v>6625329.038765344</v>
+        <v>6625325</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1239,19 +1174,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1283,15 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105928394</v>
+        <v>105928353</v>
       </c>
       <c r="B7" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,21 +1219,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1327,10 +1247,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>690839.4449161494</v>
+        <v>690853</v>
       </c>
       <c r="R7" t="n">
-        <v>6625359.983622117</v>
+        <v>6625345</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1360,19 +1280,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1407,12 +1317,7 @@
         <v>105928354</v>
       </c>
       <c r="B8" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>690913.177766592</v>
+        <v>690913</v>
       </c>
       <c r="R8" t="n">
-        <v>6625294.031789551</v>
+        <v>6625294</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1481,19 +1386,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1525,15 +1420,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105928353</v>
+        <v>105928355</v>
       </c>
       <c r="B9" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>690852.3607236912</v>
+        <v>690919</v>
       </c>
       <c r="R9" t="n">
-        <v>6625344.98153938</v>
+        <v>6625313</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1602,19 +1492,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1646,15 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>105928351</v>
+        <v>105928356</v>
       </c>
       <c r="B10" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1690,10 +1565,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>690871.6442753008</v>
+        <v>690935</v>
       </c>
       <c r="R10" t="n">
-        <v>6625324.242231154</v>
+        <v>6625329</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1723,19 +1598,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1760,6 +1625,112 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering vid Sweco</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>105928394</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Eknäs-Ledinge, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>690839</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6625360</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Rimbo</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kirsi Jokinen</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anna Broberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
         <is>
           <t>Naturvärdesinventering vid Sweco</t>
         </is>

--- a/artfynd/A 21730-2025 artfynd.xlsx
+++ b/artfynd/A 21730-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
           <t>Naturvärdesinventering vid Sweco</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105928522</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Naturvärdesinventering vid Sweco</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105928496</t>
         </is>
       </c>
     </row>
@@ -993,6 +1008,11 @@
           <t>Naturvärdesinventering vid Sweco</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105928497</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1099,6 +1119,11 @@
           <t>Naturvärdesinventering vid Sweco</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105928350</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1205,6 +1230,11 @@
           <t>Naturvärdesinventering vid Sweco</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105928351</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1311,6 +1341,11 @@
           <t>Naturvärdesinventering vid Sweco</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105928353</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1417,6 +1452,11 @@
           <t>Naturvärdesinventering vid Sweco</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105928354</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1523,6 +1563,11 @@
           <t>Naturvärdesinventering vid Sweco</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105928355</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1629,6 +1674,11 @@
           <t>Naturvärdesinventering vid Sweco</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105928356</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1735,8 +1785,25 @@
           <t>Naturvärdesinventering vid Sweco</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105928394</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>